--- a/data/trans_orig/P1417-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2007</t>
+          <t>Población con diagnóstico de anemia en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>18678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21480</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>684978</t>
+          <t>684924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670278</t>
+          <t>669673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>682975</t>
+          <t>682791</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1360883</t>
+          <t>1359865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1375400</t>
+          <t>1374934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>953553</t>
+          <t>951982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>960801</t>
+          <t>960798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>946135</t>
+          <t>946525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961827</t>
+          <t>961156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1904340</t>
+          <t>1904709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1921019</t>
+          <t>1921817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>28450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33589</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669143</t>
+          <t>668759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654232</t>
+          <t>655391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672603</t>
+          <t>672274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1328761</t>
+          <t>1329719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1348874</t>
+          <t>1348215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>25488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31635</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>931228</t>
+          <t>930914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>939999</t>
+          <t>940403</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1013643</t>
+          <t>1013124</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030276</t>
+          <t>1029174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1949199</t>
+          <t>1950166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967894</t>
+          <t>1967987</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73613</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3253841</t>
+          <t>3254465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3269786</t>
+          <t>3269199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3305584</t>
+          <t>3305020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3335927</t>
+          <t>3335588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6565780</t>
+          <t>6565794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6599602</t>
+          <t>6601654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2012</t>
+          <t>Población con diagnóstico de anemia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9574</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>27539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>699524</t>
+          <t>698133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670129</t>
+          <t>669511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>687455</t>
+          <t>687476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1372507</t>
+          <t>1372120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1389352</t>
+          <t>1389591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46219</t>
+          <t>48178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53862</t>
+          <t>54643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1002651</t>
+          <t>1003747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014843</t>
+          <t>1014821</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>982754</t>
+          <t>980795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1005902</t>
+          <t>1005600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993059</t>
+          <t>1992278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2017905</t>
+          <t>2017935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>32873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>33747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>752316</t>
+          <t>750672</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>745473</t>
+          <t>744301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764856</t>
+          <t>764233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1500152</t>
+          <t>1501050</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1521187</t>
+          <t>1520631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37123</t>
+          <t>35821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43854</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935471</t>
+          <t>935652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>944793</t>
+          <t>945641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1013732</t>
+          <t>1015034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034072</t>
+          <t>1034606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1954740</t>
+          <t>1955563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1977662</t>
+          <t>1976564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119082</t>
+          <t>118642</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136637</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3402132</t>
+          <t>3403317</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3418516</t>
+          <t>3417749</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3434970</t>
+          <t>3435410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3475702</t>
+          <t>3476253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6844194</t>
+          <t>6848596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6888647</t>
+          <t>6891216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2016</t>
+          <t>Población con diagnóstico de anemia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>30501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,47 +4677,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>25244</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>16253</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>35843</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>25244</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16478</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>37272</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662719</t>
+          <t>662643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>672972</t>
+          <t>673044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641370</t>
+          <t>642338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660243</t>
+          <t>661403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,47 +4790,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1322395</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1311796</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1331386</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1322395</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1310367</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1331161</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13546</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33187</t>
+          <t>32883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1006960</t>
+          <t>1006967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018318</t>
+          <t>1018420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1009726</t>
+          <t>1010030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1029367</t>
+          <t>1029928</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2023600</t>
+          <t>2022816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2045971</t>
+          <t>2045641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>27594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>33020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748452</t>
+          <t>748862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757738</t>
+          <t>757715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>757999</t>
+          <t>757417</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>775228</t>
+          <t>774839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1512103</t>
+          <t>1511543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1530884</t>
+          <t>1530981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>932300</t>
+          <t>932294</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002297</t>
+          <t>1002544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1025154</t>
+          <t>1025011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939940</t>
+          <t>1939733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1961533</t>
+          <t>1961949</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70053</t>
+          <t>70214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110177</t>
+          <t>107871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126421</t>
+          <t>130168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3364065</t>
+          <t>3364774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3382294</t>
+          <t>3382214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3434365</t>
+          <t>3436671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3474489</t>
+          <t>3474328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6812471</t>
+          <t>6808724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6853588</t>
+          <t>6851021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2023</t>
+          <t>Población con diagnóstico de anemia en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33155</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619687</t>
+          <t>620249</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628985</t>
+          <t>629540</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641914</t>
+          <t>641703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657137</t>
+          <t>656926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1266012</t>
+          <t>1265312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1283920</t>
+          <t>1282961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>31489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>51075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70356</t>
+          <t>70453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1168575</t>
+          <t>1168523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185148</t>
+          <t>1185671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>904190</t>
+          <t>905137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>924091</t>
+          <t>924723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2077835</t>
+          <t>2077738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2110067</t>
+          <t>2112023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>63184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>31608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68215</t>
+          <t>69980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>687256</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>698055</t>
+          <t>698133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>870611</t>
+          <t>868958</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>913942</t>
+          <t>911627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1565579</t>
+          <t>1563814</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1601076</t>
+          <t>1602186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34682</t>
+          <t>34409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57397</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65485</t>
+          <t>65687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913690</t>
+          <t>911708</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922520</t>
+          <t>922667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033375</t>
+          <t>1032456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1056090</t>
+          <t>1056363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952118</t>
+          <t>1951916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975063</t>
+          <t>1975299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124424</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179045</t>
+          <t>180486</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161067</t>
+          <t>165015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221119</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3403629</t>
+          <t>3404626</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3426763</t>
+          <t>3428124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3475149</t>
+          <t>3473708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3529770</t>
+          <t>3529567</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6887884</t>
+          <t>6889066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6947936</t>
+          <t>6943988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1417-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>19398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22498</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>684924</t>
+          <t>685301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>669673</t>
+          <t>668953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>682791</t>
+          <t>682374</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1359865</t>
+          <t>1359780</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1374934</t>
+          <t>1375239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>25847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>951982</t>
+          <t>952885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>960798</t>
+          <t>960801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>946525</t>
+          <t>946796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961156</t>
+          <t>961301</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1904709</t>
+          <t>1904346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1921817</t>
+          <t>1920721</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28450</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668759</t>
+          <t>669287</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>655391</t>
+          <t>654916</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672274</t>
+          <t>672552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1329719</t>
+          <t>1329978</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1348215</t>
+          <t>1349452</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25488</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>930914</t>
+          <t>931326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>940403</t>
+          <t>940464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1013124</t>
+          <t>1013535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029174</t>
+          <t>1030155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950166</t>
+          <t>1949537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967987</t>
+          <t>1967468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>43731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89366</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3254465</t>
+          <t>3254200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3269199</t>
+          <t>3269219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3305020</t>
+          <t>3304197</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3335588</t>
+          <t>3335466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6565794</t>
+          <t>6566375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6601654</t>
+          <t>6601682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>698133</t>
+          <t>698574</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>669511</t>
+          <t>668988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>687476</t>
+          <t>686639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1372120</t>
+          <t>1371053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1389591</t>
+          <t>1389556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48178</t>
+          <t>47105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28986</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>56786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003747</t>
+          <t>1003481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014821</t>
+          <t>1014827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>980795</t>
+          <t>981868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1005600</t>
+          <t>1005745</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1992278</t>
+          <t>1990135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2017935</t>
+          <t>2017364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>13230</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32873</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>750672</t>
+          <t>752334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>744301</t>
+          <t>744621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>764233</t>
+          <t>763944</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1501050</t>
+          <t>1501012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1520631</t>
+          <t>1521178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35821</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43031</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935652</t>
+          <t>934437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945641</t>
+          <t>944876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1015034</t>
+          <t>1014645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1034606</t>
+          <t>1034009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1955563</t>
+          <t>1953566</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1976564</t>
+          <t>1976701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77799</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>117794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132235</t>
+          <t>137955</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3403317</t>
+          <t>3402307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3417749</t>
+          <t>3418477</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3435410</t>
+          <t>3436258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3476253</t>
+          <t>3475097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6848596</t>
+          <t>6842876</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6891216</t>
+          <t>6886560</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>31611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16253</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35843</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662643</t>
+          <t>662911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673044</t>
+          <t>672903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>642338</t>
+          <t>641228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>661403</t>
+          <t>660506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1311796</t>
+          <t>1309860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331386</t>
+          <t>1330264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12985</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>43052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1006967</t>
+          <t>1007066</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018420</t>
+          <t>1018416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1010030</t>
+          <t>1011104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1029928</t>
+          <t>1029583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2022816</t>
+          <t>2022292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2045641</t>
+          <t>2044661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,82 +5328,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>17077</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>27055</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>21834</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>13873</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>33745</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17077</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10172</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27594</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>21834</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>13582</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>33020</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748862</t>
+          <t>748280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757715</t>
+          <t>757858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,82 +5441,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>767934</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>757956</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>775290</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1522729</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1510818</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1530690</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>767934</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>757417</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>774839</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>97,82%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1522729</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1511543</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1530981</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41613</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>932294</t>
+          <t>932962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1002544</t>
+          <t>1002728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1025011</t>
+          <t>1024472</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1939733</t>
+          <t>1938947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1961949</t>
+          <t>1961556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70214</t>
+          <t>68985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>106283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87871</t>
+          <t>87288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>128433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3364774</t>
+          <t>3363859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3382214</t>
+          <t>3382288</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3436671</t>
+          <t>3438259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3474328</t>
+          <t>3475557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6808724</t>
+          <t>6810459</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6851021</t>
+          <t>6851604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>28149</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33366</t>
+          <t>38756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33853</t>
+          <t>39113</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44104</t>
+          <t>50622</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>625650</t>
+          <t>678377</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620249</t>
+          <t>671050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>629540</t>
+          <t>683033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>649913</t>
+          <t>704290</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>641703</t>
+          <t>693683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656926</t>
+          <t>710998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1275563</t>
+          <t>1382669</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1265312</t>
+          <t>1371160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1282961</t>
+          <t>1391492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634347</t>
+          <t>689342</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634347</t>
+          <t>689342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634347</t>
+          <t>689342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675069</t>
+          <t>732439</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675069</t>
+          <t>732439</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675069</t>
+          <t>732439</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309416</t>
+          <t>1421782</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309416</t>
+          <t>1421782</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309416</t>
+          <t>1421782</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40542</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51075</t>
+          <t>55303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55308</t>
+          <t>60078</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36168</t>
+          <t>47756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70453</t>
+          <t>74373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1177214</t>
+          <t>1032270</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1168523</t>
+          <t>1024362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1185671</t>
+          <t>1037979</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>915670</t>
+          <t>1024398</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>905137</t>
+          <t>1013534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>924723</t>
+          <t>1033845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2092883</t>
+          <t>2056667</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2077738</t>
+          <t>2042372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2112023</t>
+          <t>2068989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191979</t>
+          <t>1047909</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191979</t>
+          <t>1047909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191979</t>
+          <t>1047909</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956212</t>
+          <t>1068837</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956212</t>
+          <t>1068837</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956212</t>
+          <t>1068837</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2148191</t>
+          <t>2116745</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2148191</t>
+          <t>2116745</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2148191</t>
+          <t>2116745</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,17 +7255,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63184</t>
+          <t>61606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>55352</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31608</t>
+          <t>42347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69980</t>
+          <t>72372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -7368,17 +7368,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>694222</t>
+          <t>791379</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>784441</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>698133</t>
+          <t>795819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,34 +7403,34 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>890572</t>
+          <t>764096</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>868958</t>
+          <t>749337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>911627</t>
+          <t>774739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>95,54%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,22%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1653</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1584794</t>
+          <t>1555475</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1563814</t>
+          <t>1538455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1602186</t>
+          <t>1568480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701652</t>
+          <t>799884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701652</t>
+          <t>799884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701652</t>
+          <t>799884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932142</t>
+          <t>810943</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932142</t>
+          <t>810943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932142</t>
+          <t>810943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1633794</t>
+          <t>1610827</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1633794</t>
+          <t>1610827</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1633794</t>
+          <t>1610827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>45806</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34409</t>
+          <t>37553</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58316</t>
+          <t>62358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>53677</t>
+          <t>57693</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65687</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>918960</t>
+          <t>981418</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911708</t>
+          <t>975029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922667</t>
+          <t>985551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1044966</t>
+          <t>1067324</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1032456</t>
+          <t>1054015</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1056363</t>
+          <t>1078820</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1963926</t>
+          <t>2048742</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951916</t>
+          <t>2035282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975299</t>
+          <t>2059731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1090772</t>
+          <t>1116373</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1090772</t>
+          <t>1116373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1090772</t>
+          <t>1116373</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017603</t>
+          <t>2106435</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017603</t>
+          <t>2106435</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017603</t>
+          <t>2106435</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50183</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124627</t>
+          <t>146499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180486</t>
+          <t>189643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>212236</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165015</t>
+          <t>189004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219937</t>
+          <t>238462</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3416046</t>
+          <t>3483444</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3404626</t>
+          <t>3470100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3428124</t>
+          <t>3493098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3501120</t>
+          <t>3560108</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3473708</t>
+          <t>3538949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3529567</t>
+          <t>3582093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6917166</t>
+          <t>7043553</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6889066</t>
+          <t>7017327</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6943988</t>
+          <t>7066785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
